--- a/Doc/GameExcels/dic_mountains.xlsx
+++ b/Doc/GameExcels/dic_mountains.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Yijue\shanhaijing·shijie\Doc\GameExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Yijue\Shanhaijing_laya\Doc\GameExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -97,7 +97,7 @@
     <t>1101&amp;1102&amp;1103&amp;1104&amp;1105</t>
   </si>
   <si>
-    <t>definition_info_1</t>
+    <t>definition_mountains_info_1</t>
   </si>
   <si>
     <t>第1章现代译文</t>
@@ -112,7 +112,7 @@
     <t>2101&amp;2102&amp;2103&amp;2104&amp;2105</t>
   </si>
   <si>
-    <t>definition_info_2</t>
+    <t>definition_mountains_info_2</t>
   </si>
   <si>
     <t>第2章现代译文</t>
@@ -127,7 +127,7 @@
     <t>3101&amp;3102&amp;3103&amp;3104&amp;3105</t>
   </si>
   <si>
-    <t>definition_info_3</t>
+    <t>definition_mountains_info_3</t>
   </si>
   <si>
     <t>第3章现代译文</t>
@@ -142,7 +142,7 @@
     <t>4101&amp;4102&amp;4103&amp;4104&amp;4105</t>
   </si>
   <si>
-    <t>definition_info_4</t>
+    <t>definition_mountains_info_4</t>
   </si>
   <si>
     <t>第4章现代译文</t>
@@ -157,7 +157,7 @@
     <t>5101&amp;5102&amp;5103&amp;5104&amp;5105</t>
   </si>
   <si>
-    <t>definition_info_5</t>
+    <t>definition_mountains_info_5</t>
   </si>
   <si>
     <t>第5章现代译文</t>
@@ -172,7 +172,7 @@
     <t>6101&amp;6102&amp;6103&amp;6104&amp;6105</t>
   </si>
   <si>
-    <t>definition_info_6</t>
+    <t>definition_mountains_info_6</t>
   </si>
   <si>
     <t>第6章现代译文</t>
@@ -187,7 +187,7 @@
     <t>7101&amp;7102&amp;7103&amp;7104&amp;7105</t>
   </si>
   <si>
-    <t>definition_info_7</t>
+    <t>definition_mountains_info_7</t>
   </si>
   <si>
     <t>第7章现代译文</t>
@@ -1199,7 +1199,7 @@
     <col min="3" max="3" width="17.625" customWidth="1"/>
     <col min="4" max="4" width="8.875" customWidth="1"/>
     <col min="5" max="5" width="30.875" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="6" max="6" width="28.25" customWidth="1"/>
     <col min="7" max="7" width="42.875" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
@@ -1282,7 +1282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" ht="27" spans="1:8">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" ht="27" spans="1:8">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" ht="27" spans="1:8">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" ht="27" spans="1:8">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" ht="27" spans="1:8">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" ht="27" spans="1:8">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" ht="27" spans="1:8">
       <c r="A10" s="4">
         <v>7</v>
       </c>

--- a/Doc/GameExcels/dic_mountains.xlsx
+++ b/Doc/GameExcels/dic_mountains.xlsx
@@ -1282,7 +1282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:8">
+    <row r="4" spans="1:8">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:8">
+    <row r="5" spans="1:8">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:8">
+    <row r="6" spans="1:8">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:8">
+    <row r="7" spans="1:8">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:8">
+    <row r="8" spans="1:8">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:8">
+    <row r="9" spans="1:8">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:8">
+    <row r="10" spans="1:8">
       <c r="A10" s="4">
         <v>7</v>
       </c>
